--- a/data/matrix_codebook.xlsx
+++ b/data/matrix_codebook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="845" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5466AC2F-965B-4439-BC55-0AA140202DDC}"/>
+  <xr:revisionPtr revIDLastSave="871" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86F05C87-0FDA-4AAB-AF31-2C6F887C1F90}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="502">
   <si>
     <t>BESSI</t>
   </si>
@@ -1509,6 +1509,42 @@
   </si>
   <si>
     <t>Use of digital assistance for change</t>
+  </si>
+  <si>
+    <t>testanxiety</t>
+  </si>
+  <si>
+    <t>Test anxiety</t>
+  </si>
+  <si>
+    <t>testanxietycontrol</t>
+  </si>
+  <si>
+    <t>Test anxiety reduction strategies</t>
+  </si>
+  <si>
+    <t>affectiveengagement</t>
+  </si>
+  <si>
+    <t>Affective engagement</t>
+  </si>
+  <si>
+    <t>behavioralengagement</t>
+  </si>
+  <si>
+    <t>Behavioral engagement</t>
+  </si>
+  <si>
+    <t>cognitiveengagement</t>
+  </si>
+  <si>
+    <t>Cognitive engagement</t>
+  </si>
+  <si>
+    <t>agenticengagement</t>
+  </si>
+  <si>
+    <t>Agentic engagement</t>
   </si>
 </sst>
 </file>
@@ -1836,14 +1872,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A8B26-530C-40CA-A676-99F1EAC2BADD}">
-  <dimension ref="A1:AO234"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AO241"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="35.81640625" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="35.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>81</v>
       </c>
@@ -1860,7 +1896,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -1911,7 +1947,7 @@
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -1925,7 +1961,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -1939,7 +1975,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -1953,7 +1989,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -1967,7 +2003,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -1981,7 +2017,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -1995,7 +2031,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>82</v>
       </c>
@@ -2009,7 +2045,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -2023,7 +2059,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>82</v>
       </c>
@@ -2037,7 +2073,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -2051,7 +2087,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -2065,7 +2101,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>82</v>
       </c>
@@ -2079,7 +2115,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -2093,7 +2129,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -2107,7 +2143,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -2121,7 +2157,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>82</v>
       </c>
@@ -2135,7 +2171,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>82</v>
       </c>
@@ -2149,7 +2185,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>82</v>
       </c>
@@ -2163,7 +2199,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>82</v>
       </c>
@@ -2177,7 +2213,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>82</v>
       </c>
@@ -2191,7 +2227,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -2205,7 +2241,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -2219,7 +2255,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -2233,7 +2269,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>82</v>
       </c>
@@ -2247,7 +2283,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>82</v>
       </c>
@@ -2261,7 +2297,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -2275,7 +2311,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>82</v>
       </c>
@@ -2289,7 +2325,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -2303,7 +2339,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>82</v>
       </c>
@@ -2317,7 +2353,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>82</v>
       </c>
@@ -2331,7 +2367,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>82</v>
       </c>
@@ -2345,7 +2381,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -2359,7 +2395,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2373,7 +2409,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -2387,7 +2423,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -2401,7 +2437,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>82</v>
       </c>
@@ -2415,7 +2451,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -2468,7 +2504,7 @@
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -2485,7 +2521,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -2502,7 +2538,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -2519,7 +2555,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -2536,12 +2572,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.3">
       <c r="B45" s="2"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>328</v>
       </c>
@@ -2555,7 +2591,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>328</v>
       </c>
@@ -2569,7 +2605,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>328</v>
       </c>
@@ -2583,7 +2619,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>328</v>
       </c>
@@ -2597,7 +2633,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>328</v>
       </c>
@@ -2611,7 +2647,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>328</v>
       </c>
@@ -2625,7 +2661,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>328</v>
       </c>
@@ -2639,7 +2675,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>328</v>
       </c>
@@ -2653,7 +2689,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>328</v>
       </c>
@@ -2667,7 +2703,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>328</v>
       </c>
@@ -2681,7 +2717,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>328</v>
       </c>
@@ -2695,7 +2731,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>328</v>
       </c>
@@ -2709,7 +2745,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>328</v>
       </c>
@@ -2723,7 +2759,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>328</v>
       </c>
@@ -2737,7 +2773,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>328</v>
       </c>
@@ -2751,7 +2787,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>328</v>
       </c>
@@ -2765,7 +2801,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>328</v>
       </c>
@@ -2779,7 +2815,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>328</v>
       </c>
@@ -2793,7 +2829,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>328</v>
       </c>
@@ -2807,7 +2843,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>328</v>
       </c>
@@ -2821,7 +2857,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>328</v>
       </c>
@@ -2835,7 +2871,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>328</v>
       </c>
@@ -2849,14 +2885,14 @@
         <v>386</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B68" s="2"/>
       <c r="D68" s="1"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B69" s="2"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -2870,7 +2906,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -2884,7 +2920,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -2898,7 +2934,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -2912,7 +2948,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2926,7 +2962,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -2940,7 +2976,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -2954,7 +2990,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>83</v>
       </c>
@@ -2968,7 +3004,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2982,7 +3018,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -2996,7 +3032,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -3010,7 +3046,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -3024,7 +3060,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -3038,7 +3074,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -3052,7 +3088,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -3066,7 +3102,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -3080,7 +3116,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>83</v>
       </c>
@@ -3094,7 +3130,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>83</v>
       </c>
@@ -3108,7 +3144,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>83</v>
       </c>
@@ -3122,7 +3158,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>83</v>
       </c>
@@ -3136,13 +3172,13 @@
         <v>245</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>83</v>
       </c>
       <c r="B90" s="2"/>
     </row>
-    <row r="91" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>83</v>
       </c>
@@ -3156,7 +3192,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -3170,7 +3206,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>83</v>
       </c>
@@ -3184,7 +3220,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>83</v>
       </c>
@@ -3198,7 +3234,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>83</v>
       </c>
@@ -3212,7 +3248,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>83</v>
       </c>
@@ -3226,7 +3262,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>83</v>
       </c>
@@ -3234,7 +3270,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>83</v>
       </c>
@@ -3248,7 +3284,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>83</v>
       </c>
@@ -3262,7 +3298,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>83</v>
       </c>
@@ -3276,7 +3312,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>83</v>
       </c>
@@ -3290,7 +3326,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>83</v>
       </c>
@@ -3304,7 +3340,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>83</v>
       </c>
@@ -3318,7 +3354,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>83</v>
       </c>
@@ -3332,7 +3368,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>83</v>
       </c>
@@ -3346,7 +3382,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>83</v>
       </c>
@@ -3360,7 +3396,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>83</v>
       </c>
@@ -3374,7 +3410,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>83</v>
       </c>
@@ -3388,7 +3424,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>83</v>
       </c>
@@ -3402,7 +3438,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>83</v>
       </c>
@@ -3416,7 +3452,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>83</v>
       </c>
@@ -3430,7 +3466,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>83</v>
       </c>
@@ -3444,18 +3480,18 @@
         <v>266</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B113" s="2"/>
       <c r="D113" s="1"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B114" s="2"/>
       <c r="D114" s="1"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B115" s="2"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>84</v>
       </c>
@@ -3472,7 +3508,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>84</v>
       </c>
@@ -3486,7 +3522,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>84</v>
       </c>
@@ -3503,7 +3539,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>84</v>
       </c>
@@ -3517,7 +3553,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>84</v>
       </c>
@@ -3525,13 +3561,13 @@
         <v>15</v>
       </c>
       <c r="C120" t="s">
-        <v>98</v>
+        <v>494</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>84</v>
       </c>
@@ -3539,13 +3575,13 @@
         <v>15</v>
       </c>
       <c r="C121" t="s">
-        <v>99</v>
+        <v>496</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>84</v>
       </c>
@@ -3553,13 +3589,13 @@
         <v>15</v>
       </c>
       <c r="C122" t="s">
-        <v>310</v>
+        <v>498</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>84</v>
       </c>
@@ -3567,14 +3603,13 @@
         <v>15</v>
       </c>
       <c r="C123" t="s">
-        <v>334</v>
+        <v>500</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="G123" s="2"/>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>84</v>
       </c>
@@ -3582,13 +3617,13 @@
         <v>15</v>
       </c>
       <c r="C124" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>84</v>
       </c>
@@ -3596,14 +3631,13 @@
         <v>15</v>
       </c>
       <c r="C125" t="s">
-        <v>340</v>
+        <v>99</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="J125" s="2"/>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>84</v>
       </c>
@@ -3611,13 +3645,13 @@
         <v>15</v>
       </c>
       <c r="C126" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>84</v>
       </c>
@@ -3625,13 +3659,14 @@
         <v>15</v>
       </c>
       <c r="C127" t="s">
-        <v>387</v>
+        <v>334</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+        <v>335</v>
+      </c>
+      <c r="G127" s="2"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>84</v>
       </c>
@@ -3639,1285 +3674,1374 @@
         <v>15</v>
       </c>
       <c r="C128" t="s">
-        <v>389</v>
+        <v>339</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>84</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>364</v>
+        <v>15</v>
       </c>
       <c r="C129" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+      <c r="J129" s="2"/>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>84</v>
       </c>
       <c r="B130" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C130" t="s">
+        <v>341</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>84</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C131" t="s">
+        <v>387</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>84</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C132" t="s">
+        <v>389</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>84</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C133" t="s">
+        <v>490</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>84</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C134" t="s">
+        <v>492</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>84</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C135" t="s">
+        <v>365</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>84</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C136" t="s">
         <v>367</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B131" s="2"/>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>85</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C132" t="s">
-        <v>52</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>85</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C133" t="s">
-        <v>391</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>85</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C134" t="s">
-        <v>401</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>85</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C135" t="s">
-        <v>451</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>85</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C136" t="s">
-        <v>452</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>85</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C137" t="s">
-        <v>121</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>85</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C138" t="s">
-        <v>122</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B137" s="2"/>
+      <c r="D137" s="1"/>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B138" s="2"/>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>85</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C139" t="s">
-        <v>395</v>
+        <v>52</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>85</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="C140" t="s">
-        <v>66</v>
+        <v>391</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>85</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="C141" t="s">
-        <v>67</v>
+        <v>401</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>85</v>
       </c>
       <c r="B142" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C142" t="s">
+        <v>451</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>85</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C143" t="s">
+        <v>452</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>85</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144" t="s">
+        <v>121</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>85</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C145" t="s">
+        <v>122</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>85</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" t="s">
+        <v>395</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>85</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C147" t="s">
+        <v>66</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>85</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C148" t="s">
+        <v>67</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>85</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C149" t="s">
         <v>455</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D149" s="1" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B143" s="2"/>
-      <c r="D143" s="1"/>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B144" s="2"/>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B150" s="2"/>
+      <c r="D150" s="1"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B151" s="2"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
         <v>86</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B152" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C152" t="s">
         <v>54</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="D152" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E152" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
         <v>86</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="B153" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C153" t="s">
         <v>79</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="D153" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
         <v>86</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="B154" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C154" t="s">
         <v>345</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="D154" s="1" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B148" s="2"/>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B155" s="2"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
         <v>87</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B156" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C156" t="s">
         <v>58</v>
       </c>
-      <c r="D149" s="1" t="s">
+      <c r="D156" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
         <v>87</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="B157" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C157" t="s">
         <v>59</v>
       </c>
-      <c r="D150" s="1" t="s">
+      <c r="D157" s="1" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
         <v>87</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B158" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C158" t="s">
         <v>60</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="D158" s="1" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
         <v>87</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="B159" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C159" t="s">
         <v>61</v>
       </c>
-      <c r="D152" s="1" t="s">
+      <c r="D159" s="1" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
         <v>87</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="B160" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C160" t="s">
         <v>356</v>
       </c>
-      <c r="D153" s="1" t="s">
+      <c r="D160" s="1" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
         <v>87</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="B161" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C161" t="s">
         <v>313</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="D161" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B155" s="2"/>
-      <c r="D155" s="1"/>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B156" s="2"/>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>88</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C157" t="s">
-        <v>107</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>88</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C158" t="s">
-        <v>397</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
-        <v>88</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C159" t="s">
-        <v>108</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>88</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C160" t="s">
-        <v>109</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
-        <v>88</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C161" t="s">
-        <v>110</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
-        <v>88</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C162" t="s">
-        <v>167</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A163" t="s">
-        <v>88</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C163" t="s">
-        <v>393</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B162" s="2"/>
+      <c r="D162" s="1"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B163" s="2"/>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>88</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C164" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>88</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C165" t="s">
-        <v>80</v>
+        <v>397</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>88</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C166" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>88</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C167" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>88</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C168" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>88</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C169" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>88</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C170" t="s">
-        <v>117</v>
+        <v>393</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>88</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>316</v>
+        <v>111</v>
       </c>
       <c r="C171" t="s">
-        <v>315</v>
+        <v>112</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>88</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C172" t="s">
+        <v>80</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>88</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C173" t="s">
+        <v>113</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>88</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C174" t="s">
+        <v>114</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>88</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C175" t="s">
+        <v>115</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>88</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C176" t="s">
+        <v>116</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>88</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C177" t="s">
+        <v>117</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>88</v>
+      </c>
+      <c r="B178" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C178" t="s">
+        <v>315</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>88</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C179" t="s">
         <v>318</v>
       </c>
-      <c r="D172" s="1" t="s">
+      <c r="D179" s="1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B173" s="2"/>
-      <c r="D173" s="1"/>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B174" s="2"/>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A175" t="s">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B180" s="2"/>
+      <c r="D180" s="1"/>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B181" s="2"/>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
         <v>89</v>
       </c>
-      <c r="B175" s="2" t="s">
+      <c r="B182" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C182" t="s">
         <v>101</v>
       </c>
-      <c r="D175" s="1" t="s">
+      <c r="D182" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A176" t="s">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
         <v>89</v>
       </c>
-      <c r="B176" s="2" t="s">
+      <c r="B183" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C183" t="s">
         <v>102</v>
       </c>
-      <c r="D176" s="1" t="s">
+      <c r="D183" s="1" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A177" t="s">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
         <v>89</v>
       </c>
-      <c r="B177" s="2" t="s">
+      <c r="B184" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C184" t="s">
         <v>103</v>
       </c>
-      <c r="D177" s="1" t="s">
+      <c r="D184" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
         <v>89</v>
       </c>
-      <c r="B178" s="2" t="s">
+      <c r="B185" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C185" t="s">
         <v>104</v>
       </c>
-      <c r="D178" s="1" t="s">
+      <c r="D185" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A179" t="s">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
         <v>89</v>
       </c>
-      <c r="B179" s="2" t="s">
+      <c r="B186" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C186" t="s">
         <v>105</v>
       </c>
-      <c r="D179" s="1" t="s">
+      <c r="D186" s="1" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A180" t="s">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
         <v>89</v>
       </c>
-      <c r="B180" s="2" t="s">
+      <c r="B187" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C187" t="s">
         <v>106</v>
       </c>
-      <c r="D180" s="1" t="s">
+      <c r="D187" s="1" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B181" s="2"/>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A182" t="s">
-        <v>90</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C182" t="s">
-        <v>63</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A183" t="s">
-        <v>90</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C183" t="s">
-        <v>449</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A184" t="s">
-        <v>90</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C184" t="s">
-        <v>65</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A185" t="s">
-        <v>90</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C185" t="s">
-        <v>336</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A186" t="s">
-        <v>90</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C186" t="s">
-        <v>348</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A187" t="s">
-        <v>90</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C187" t="s">
-        <v>351</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A188" t="s">
-        <v>90</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C188" t="s">
-        <v>354</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B188" s="2"/>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>90</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>407</v>
+        <v>62</v>
       </c>
       <c r="C189" t="s">
-        <v>408</v>
+        <v>63</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>90</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="C190" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>90</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>415</v>
+        <v>64</v>
       </c>
       <c r="C191" t="s">
-        <v>413</v>
+        <v>65</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>90</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>415</v>
+        <v>347</v>
       </c>
       <c r="C192" t="s">
-        <v>417</v>
+        <v>336</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>90</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>418</v>
+        <v>347</v>
       </c>
       <c r="C193" t="s">
-        <v>420</v>
+        <v>348</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>90</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>421</v>
+        <v>350</v>
       </c>
       <c r="C194" t="s">
-        <v>422</v>
+        <v>351</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>90</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>424</v>
+        <v>353</v>
       </c>
       <c r="C195" t="s">
-        <v>426</v>
+        <v>354</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>90</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C196" t="s">
+        <v>408</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>90</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C197" t="s">
+        <v>410</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>90</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C198" t="s">
+        <v>413</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>90</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C199" t="s">
+        <v>417</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>90</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C200" t="s">
+        <v>420</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>90</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C201" t="s">
+        <v>422</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>90</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C202" t="s">
+        <v>426</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>90</v>
+      </c>
+      <c r="B203" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C203" t="s">
         <v>429</v>
       </c>
-      <c r="D196" s="1" t="s">
+      <c r="D203" s="1" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B197" s="2"/>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A198" t="s">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B204" s="2"/>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
         <v>118</v>
       </c>
-      <c r="B198" s="2" t="s">
+      <c r="B205" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C198" t="s">
+      <c r="C205" t="s">
         <v>120</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="D205" s="1" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A199" t="s">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
         <v>118</v>
       </c>
-      <c r="B199" s="2" t="s">
+      <c r="B206" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C199" t="s">
+      <c r="C206" t="s">
         <v>399</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="D206" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A201" t="s">
-        <v>320</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C201" t="s">
-        <v>322</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A202" t="s">
-        <v>320</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C202" t="s">
-        <v>323</v>
-      </c>
-      <c r="D202" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A203" t="s">
-        <v>320</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C203" t="s">
-        <v>324</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B204" s="2"/>
-      <c r="D204" s="1"/>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A205" t="s">
-        <v>320</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C205" t="s">
-        <v>434</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A206" t="s">
-        <v>320</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C206" t="s">
-        <v>435</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A207" t="s">
-        <v>320</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C207" t="s">
-        <v>436</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>320</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>438</v>
+        <v>321</v>
       </c>
       <c r="C208" t="s">
-        <v>437</v>
+        <v>322</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B209" s="2"/>
-      <c r="D209" s="1"/>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>320</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C209" t="s">
+        <v>323</v>
+      </c>
+      <c r="D209" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>320</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>439</v>
+        <v>321</v>
       </c>
       <c r="C210" t="s">
-        <v>440</v>
+        <v>324</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A211" t="s">
-        <v>320</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C211" t="s">
-        <v>443</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B211" s="2"/>
+      <c r="D211" s="1"/>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>320</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C212" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>320</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C213" t="s">
+        <v>435</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>320</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C214" t="s">
+        <v>436</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>320</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C215" t="s">
+        <v>437</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B216" s="2"/>
+      <c r="D216" s="1"/>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>320</v>
+      </c>
+      <c r="B217" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C213" t="s">
+      <c r="C217" t="s">
+        <v>440</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>320</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C218" t="s">
+        <v>443</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>320</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C219" t="s">
+        <v>444</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>320</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C220" t="s">
         <v>446</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="D220" s="1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A215" t="s">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
         <v>358</v>
       </c>
-      <c r="B215" s="2" t="s">
+      <c r="B222" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C215" t="s">
+      <c r="C222" t="s">
         <v>361</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="D222" s="1" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A216" t="s">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
         <v>358</v>
       </c>
-      <c r="B216" s="2" t="s">
+      <c r="B223" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C216" t="s">
+      <c r="C223" t="s">
         <v>363</v>
       </c>
-      <c r="D216" s="1" t="s">
+      <c r="D223" s="1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A218" t="s">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
         <v>403</v>
       </c>
-      <c r="B218" s="2" t="s">
+      <c r="B225" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C218" t="s">
+      <c r="C225" t="s">
         <v>405</v>
       </c>
-      <c r="D218" s="1" t="s">
+      <c r="D225" s="1" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A220" t="s">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
         <v>458</v>
       </c>
-      <c r="B220" s="2" t="s">
+      <c r="B227" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="C220" t="s">
+      <c r="C227" t="s">
         <v>460</v>
       </c>
-      <c r="D220" s="1" t="s">
+      <c r="D227" s="1" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A222" t="s">
-        <v>461</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C222" t="s">
-        <v>463</v>
-      </c>
-      <c r="D222" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A223" t="s">
-        <v>461</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C223" t="s">
-        <v>464</v>
-      </c>
-      <c r="D223" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A224" t="s">
-        <v>461</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C224" t="s">
-        <v>465</v>
-      </c>
-      <c r="D224" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A225" t="s">
-        <v>461</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C225" t="s">
-        <v>466</v>
-      </c>
-      <c r="D225" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A226" t="s">
-        <v>461</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C226" t="s">
-        <v>467</v>
-      </c>
-      <c r="D226" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A227" t="s">
-        <v>461</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C227" t="s">
-        <v>468</v>
-      </c>
-      <c r="D227" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A228" t="s">
-        <v>461</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="C228" t="s">
-        <v>470</v>
-      </c>
-      <c r="D228" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>461</v>
       </c>
       <c r="B229" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C229" t="s">
+        <v>463</v>
+      </c>
+      <c r="D229" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>461</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C230" t="s">
+        <v>464</v>
+      </c>
+      <c r="D230" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>461</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C231" t="s">
+        <v>465</v>
+      </c>
+      <c r="D231" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>461</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C232" t="s">
+        <v>466</v>
+      </c>
+      <c r="D232" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>461</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C233" t="s">
+        <v>467</v>
+      </c>
+      <c r="D233" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>461</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C234" t="s">
+        <v>468</v>
+      </c>
+      <c r="D234" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>461</v>
+      </c>
+      <c r="B235" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="C229" t="s">
+      <c r="C235" t="s">
+        <v>470</v>
+      </c>
+      <c r="D235" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>461</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C236" t="s">
         <v>471</v>
       </c>
-      <c r="D229" t="s">
+      <c r="D236" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A231" t="s">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
         <v>480</v>
       </c>
-      <c r="B231" s="2" t="s">
+      <c r="B238" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C231" t="s">
+      <c r="C238" t="s">
         <v>485</v>
       </c>
-      <c r="D231" t="s">
+      <c r="D238" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A232" t="s">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
         <v>480</v>
       </c>
-      <c r="B232" s="2" t="s">
+      <c r="B239" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C232" t="s">
+      <c r="C239" t="s">
         <v>482</v>
       </c>
-      <c r="D232" t="s">
+      <c r="D239" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A233" t="s">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
         <v>480</v>
       </c>
-      <c r="B233" s="2" t="s">
+      <c r="B240" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C233" t="s">
+      <c r="C240" t="s">
         <v>483</v>
       </c>
-      <c r="D233" t="s">
+      <c r="D240" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A234" t="s">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
         <v>480</v>
       </c>
-      <c r="B234" s="2" t="s">
+      <c r="B241" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C234" t="s">
+      <c r="C241" t="s">
         <v>484</v>
       </c>
-      <c r="D234" t="s">
+      <c r="D241" t="s">
         <v>489</v>
       </c>
     </row>
